--- a/class_diagram/kyoutu/クラス図_面談予約sys（共通）_最新.xlsx
+++ b/class_diagram/kyoutu/クラス図_面談予約sys（共通）_最新.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20357"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCD91DA-75E6-46D2-891A-B93FA6CA4BE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{7DCD91DA-75E6-46D2-891A-B93FA6CA4BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FD25ADE-F636-4CBC-A8DC-93C66E02B3EC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18945" windowHeight="11190" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18945" windowHeight="11190" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller.GetHash" sheetId="3" r:id="rId1"/>
-    <sheet name="model.ReseInfo" sheetId="4" r:id="rId2"/>
-    <sheet name="controller.EmailSend" sheetId="5" r:id="rId3"/>
+    <sheet name="model.PastInfo" sheetId="7" r:id="rId2"/>
+    <sheet name="model.ReseInfo" sheetId="6" r:id="rId3"/>
+    <sheet name="model.BaseInfo" sheetId="4" r:id="rId4"/>
+    <sheet name="controller.EmailSend" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -28,7 +41,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +491,2577 @@
         <xdr:cNvPr id="2" name="四角形 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28050C45-3FC6-42E3-8C32-9CCC0C6F0D38}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="3362325"/>
+          <a:ext cx="5495925" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>PastInfo extends BaseInfo</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{096A9836-C118-436A-A355-E6F5FFF1D4B7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{28050C45-3FC6-42E3-8C32-9CCC0C6F0D38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="3962400"/>
+          <a:ext cx="5486400" cy="6800850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- pastID : int</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6F9DC0F-2616-4E36-8AD1-6558957DE394}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{096A9836-C118-436A-A355-E6F5FFF1D4B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="10744200"/>
+          <a:ext cx="5486400" cy="6343650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ PastInfo(pastID : int, date : DATE, startTime : int,  userName : String,  interviewerName : String, createDateTime : DATETIME, updateDateTime : DATETIME)  (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>コンストラクタ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getPastID() : int</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getDate() : DATE</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setDate(date : DATE) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getStartTime() : int</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+  setStartTime(stratTime : int) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getUserName() : String</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setUserName(userName : String) :  void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getInterviewerName() : String</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setInterviewerName(interviewerName : String) :  void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getCreateDateTime() : DATETIME</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setCreateDateTime(createDateTime : DATETIME) : void </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getUpdateDateTime() : DATETIME</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setUpdateDateTime(updateDateTime : DATETIME) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBE5D18E-A254-456F-9A53-441339A640B6}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="3590925"/>
+          <a:ext cx="5495925" cy="714375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ReseInfo extends BaseInfo</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10BFE4F9-8333-4984-83C3-31A4D560662D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EBE5D18E-A254-456F-9A53-441339A640B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="4305300"/>
+          <a:ext cx="5486400" cy="8096250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- reseID : int</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- url : String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CBDADB9-844B-4DA7-9705-DC12AB8B7A3F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{10BFE4F9-8333-4984-83C3-31A4D560662D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="12344400"/>
+          <a:ext cx="5486400" cy="7562850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ ReseInfo(reseID : int, url : String, date : DATE, startTime : int,  userName : String,  interviewerName : String, createDateTime : DATETIME, updateDateTime : DATETIME)  (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>コンストラクタ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getReseID() : int</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getURL() : String</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getDate() : DATE</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setDate(date : DATE) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getStartTime() : int</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+  setStartTime(stratTime : int) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getUserName() : String</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setUserName(userName : String) :  void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getInterviewerName() : String</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setInterviewerName(interviewerName : String) :  void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getCreateDateTime() : DATETIME</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setCreateDateTime(createDateTime : DATETIME) : void </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ getUpdateDateTime() : DATETIME</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>+ setUpdateDateTime(updateDateTime : DATETIME) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4EB8EEC-3914-4A5E-85C0-A136713226EC}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
@@ -620,7 +3204,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>ReseInfo</a:t>
+            <a:t>BaseInfo</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -785,65 +3369,23 @@
           </a:lvl9pPr>
         </a:lstStyle>
         <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>- reseID : int</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>- url : String</a:t>
-          </a:r>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr marL="0" marR="0" indent="0" algn="l">
@@ -1280,7 +3822,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>+ ReseInfo(reseID : int, url : String, date : DATE, startTime : int,  userName : String,  interviewerName : String, createDateTime : DATETIME, updateDateTime : DATETIME)  (</a:t>
+            <a:t>+ BaseInfo(date : DATE, startTime : int,  userName : String,  interviewerName : String, createDateTime : DATETIME, updateDateTime : DATETIME)  (</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
@@ -1302,7 +3844,17 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
           <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
@@ -1322,6 +3874,25 @@
               <a:spcPts val="0"/>
             </a:spcAft>
           </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
           <a:r>
             <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -1338,161 +3909,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>getReseID() : int</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>+ setReseID(reseID : int) : void</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>+ getURL() : String</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>+ setURL(url : String ) : void</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>+ getDate() : DATE</a:t>
+            <a:t>getDate() : DATE</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2019,7 +4436,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2882,33 +5299,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0986D7BF-C490-4E52-9D87-59D6F678DA9C}">
   <dimension ref="C5:O35"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="5" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="5" spans="3:15" ht="76.5">
       <c r="C5" s="1"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15">
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15">
       <c r="K9" s="6"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15">
       <c r="K10" s="6"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15">
       <c r="K11" s="7"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="13" spans="3:15">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -2918,7 +5335,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:15">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -2928,7 +5345,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:15">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2938,7 +5355,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:15">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2948,7 +5365,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:10">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -2958,7 +5375,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:10">
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -2968,7 +5385,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:10">
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -2978,7 +5395,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:10">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2988,7 +5405,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:10">
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -2998,7 +5415,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:10">
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -3008,7 +5425,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:10">
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -3018,7 +5435,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:10">
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -3028,7 +5445,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:10">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -3038,7 +5455,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:10">
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -3048,7 +5465,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:10">
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -3058,7 +5475,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:10">
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -3068,7 +5485,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:10">
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -3078,7 +5495,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:10">
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -3088,7 +5505,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:10">
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -3098,7 +5515,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:10">
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -3108,7 +5525,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:10">
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -3118,7 +5535,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:10">
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -3128,7 +5545,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:10">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -3149,28 +5566,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D51E7F2-AB93-4D20-8265-927317DBB65A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC196F-07B3-4CEA-B4A6-3898636A56D1}">
   <dimension ref="C5:O11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="5" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="5" spans="3:15" ht="76.5">
       <c r="C5" s="1"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15" ht="18.75">
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15" ht="18.75">
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15" ht="18.75">
       <c r="K9" s="6"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15" ht="18.75">
       <c r="K10" s="6"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15" ht="18.75">
       <c r="K11" s="7"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -3188,9 +5605,87 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98CE52EF-31E6-4210-A5EC-F8250E960B01}">
+  <dimension ref="C5:O11"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="5" spans="3:15" ht="76.5">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="7" spans="3:15" ht="18.75">
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="3:15" ht="18.75">
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="3:15" ht="18.75">
+      <c r="K9" s="6"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="3:15" ht="18.75">
+      <c r="K10" s="6"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="3:15" ht="18.75">
+      <c r="K11" s="7"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L11:O11"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D51E7F2-AB93-4D20-8265-927317DBB65A}">
+  <dimension ref="C5:O11"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="5" spans="3:15" ht="76.5">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="7" spans="3:15">
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="3:15">
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="3:15">
+      <c r="K9" s="6"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="3:15">
+      <c r="K10" s="6"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="3:15">
+      <c r="K11" s="7"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L11:O11"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC254A-7703-43D2-AA73-249B29D53851}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
